--- a/chipMaps/SurugaTest.xlsx
+++ b/chipMaps/SurugaTest.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\lab_repos\SurugaSeikiHex\chipMaps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E072ECD5-243D-4AA5-9F72-378FBB6A223C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125AC679-8BD9-4DE4-A3F6-689B99C97892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -212,24 +212,6 @@
     <dxf>
       <font>
         <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <strike val="0"/>
         <condense val="0"/>
         <extend val="0"/>
@@ -255,6 +237,24 @@
         <name val="Calibri"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -269,7 +269,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:D5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D5">
     <sortCondition ref="A1:A5"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:G10" totalsRowShown="0" headerRowDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="Table2" displayName="Table2" ref="A1:G10" totalsRowShown="0" headerRowDxfId="0">
   <autoFilter ref="A1:G10" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G27">
     <sortCondition ref="A1:A27"/>
@@ -304,7 +304,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{486EAC1C-C7A5-4D95-8C4D-AB245013AAC2}" name="Table4" displayName="Table4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{486EAC1C-C7A5-4D95-8C4D-AB245013AAC2}" name="Table4" displayName="Table4" ref="A1:E6" totalsRowShown="0" headerRowDxfId="2">
   <autoFilter ref="A1:E6" xr:uid="{486EAC1C-C7A5-4D95-8C4D-AB245013AAC2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{7E111667-28E0-4309-A63B-C9DF15925132}" name="Device"/>
